--- a/data/11507/各系核定經費及各類經費明細與系所代碼.xlsx
+++ b/data/11507/各系核定經費及各類經費明細與系所代碼.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\projects\BudgetDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09949E15-5FC5-4089-9F9F-F7B5424DA8BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1379A20F-8062-4830-B6FA-9CBE35DECC49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DEB7F6D8-750E-40F3-B511-66BA571B0662}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="135">
   <si>
     <t>總計</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1579,17 +1579,23 @@
   </si>
   <si>
     <r>
-      <t>1.(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>設備費</t>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="4"/>
+      </rPr>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>以業務費</t>
     </r>
     <r>
       <rPr>
@@ -1598,17 +1604,17 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>+5723)114</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>年國企系設備費超支</t>
+      <t>-173,800</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>元與工管系交換無形資產</t>
     </r>
     <r>
       <rPr>
@@ -1617,36 +1623,98 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>$5723</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>，向風管系借，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
+      <t>173,800</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve">
+2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>國企系以設備費6000與會資系交換業務費6000元</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Times New Roman"/>
+        <family val="4"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>月金融系授權無形資產</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>115</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>年國企系還</t>
+      <t>260000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>至國企系</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>設備費</t>
     </r>
     <r>
       <rPr>
@@ -1655,6 +1723,63 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
+      <t>+5723)114</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年國企系設備費超支</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>$5723</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，向風管系借，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>115</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年國企系還</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
       <t>$5723
 2.(</t>
     </r>
@@ -1745,54 +1870,69 @@
       </rPr>
       <t>與風管系交換業務費</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1.(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>設備費</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>-5723)114</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>年設備費超支</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
+      <t xml:space="preserve">
+4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>8月風管系授權無形資產</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>$5723</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>，向風管系借，</t>
+      <t>300000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>至國企系</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>設備費</t>
     </r>
     <r>
       <rPr>
@@ -1800,16 +1940,16 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>115</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>年還</t>
+      <t>-5723)114</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年設備費超支</t>
     </r>
     <r>
       <rPr>
@@ -1817,6 +1957,40 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
+      <t>$5723</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，向風管系借，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>115</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年還</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
       <t>$5723
 2.</t>
     </r>
@@ -2062,86 +2236,52 @@
       </rPr>
       <t>元</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="4"/>
-      </rPr>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>以業務費</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>-173,800</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>元與工管系交換無形資產</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
+      <t xml:space="preserve">
+7.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>173,800</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>元</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
+        <family val="4"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>月金融系、風管系授權無形資產共</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
         <rFont val="Times New Roman"/>
         <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve">
-2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>國企系以設備費6000與會資系交換業務費6000元</t>
+      </rPr>
+      <t>560000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>至國企系</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2154,7 +2294,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2248,6 +2388,19 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="4"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0070C0"/>
+      <name val="標楷體"/>
+      <family val="4"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0070C0"/>
       <name val="Times New Roman"/>
       <family val="4"/>
     </font>
@@ -3987,17 +4140,20 @@
       <c r="L14" s="21">
         <v>0</v>
       </c>
-      <c r="M14" s="21">
-        <v>680000</v>
+      <c r="M14" s="31">
+        <f>680000-260000</f>
+        <v>420000</v>
       </c>
       <c r="N14" s="20">
         <v>720000</v>
       </c>
       <c r="O14" s="8">
         <f t="shared" si="3"/>
-        <v>2000000</v>
-      </c>
-      <c r="P14" s="28"/>
+        <v>1740000</v>
+      </c>
+      <c r="P14" s="28" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="15" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="27" t="s">
@@ -4051,7 +4207,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="82.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="99" x14ac:dyDescent="0.25">
       <c r="A16" s="27" t="s">
         <v>44</v>
       </c>
@@ -4089,8 +4245,9 @@
       <c r="L16" s="21">
         <v>0</v>
       </c>
-      <c r="M16" s="21">
-        <v>300000</v>
+      <c r="M16" s="31">
+        <f>300000-300000</f>
+        <v>0</v>
       </c>
       <c r="N16" s="30">
         <f>1100000+5723</f>
@@ -4098,10 +4255,10 @@
       </c>
       <c r="O16" s="8">
         <f t="shared" si="3"/>
-        <v>1954152</v>
+        <v>1654152</v>
       </c>
       <c r="P16" s="33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4570,7 +4727,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="115.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" ht="132" x14ac:dyDescent="0.25">
       <c r="A26" s="27" t="s">
         <v>44</v>
       </c>
@@ -4612,8 +4769,9 @@
       <c r="L26" s="21">
         <v>0</v>
       </c>
-      <c r="M26" s="21">
-        <v>700000</v>
+      <c r="M26" s="31">
+        <f>700000+300000+260000</f>
+        <v>1260000</v>
       </c>
       <c r="N26" s="30">
         <f>700000-5723-26415-6000</f>
@@ -4621,10 +4779,10 @@
       </c>
       <c r="O26" s="8">
         <f t="shared" si="3"/>
-        <v>1916619</v>
+        <v>2476619</v>
       </c>
       <c r="P26" s="29" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4785,7 +4943,7 @@
         <v>2000000</v>
       </c>
       <c r="P29" s="58" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
